--- a/outputs/issues/issue_label_frequency.xlsx
+++ b/outputs/issues/issue_label_frequency.xlsx
@@ -435,7 +435,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/issues/issue_label_frequency.xlsx
+++ b/outputs/issues/issue_label_frequency.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Service Issues</t>
+          <t>Crowd and Wait Time</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -441,7 +441,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Crowd and Wait Time</t>
+          <t>Service Issues</t>
         </is>
       </c>
       <c r="B3" t="n">
